--- a/appium-tests/Appium_Mobile_E2E_300_TestCases_Analysis_Report.xlsx
+++ b/appium-tests/Appium_Mobile_E2E_300_TestCases_Analysis_Report.xlsx
@@ -431,7 +431,7 @@
         <v>Test Execution Timestamp</v>
       </c>
       <c r="B4" t="str">
-        <v>7/21/2026, 10:07:50 PM</v>
+        <v>7/21/2026, 10:25:16 PM</v>
       </c>
     </row>
     <row r="5">
